--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484582_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484582_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1383</v>
+        <v>7.1301</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4553</v>
+        <v>6.9758</v>
       </c>
       <c r="F2" t="n">
-        <v>1.683</v>
+        <v>0.1543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7419</v>
+        <v>7.7494</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4121</v>
+        <v>0.9823</v>
       </c>
       <c r="I2" t="n">
-        <v>2.154</v>
+        <v>6.7671</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7421</v>
+        <v>8.0259</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1327</v>
+        <v>2.1241</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6094</v>
+        <v>5.9018</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0002</v>
+        <v>-0.2765</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5448</v>
+        <v>-1.1418</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5446</v>
+        <v>0.8653</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>4.119</v>
+        <v>-0.4257</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4963</v>
+        <v>0.0494</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6227</v>
+        <v>-0.4751</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9109</v>
+        <v>-0.0104</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2328</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3219</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4893</v>
+        <v>4.7331</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6323</v>
+        <v>1.9098</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.143</v>
+        <v>2.8233</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7494</v>
+        <v>2.967</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9823</v>
+        <v>2.095</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7671</v>
+        <v>0.872</v>
       </c>
       <c r="J3" t="n">
-        <v>8.0259</v>
+        <v>3.0268</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1241</v>
+        <v>2.8919</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9018</v>
+        <v>0.1349</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2765</v>
+        <v>-0.0597</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1418</v>
+        <v>-0.7968</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8653</v>
+        <v>0.7371</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0665</v>
+        <v>0.1876</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2941</v>
+        <v>-0.0565</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7724</v>
+        <v>0.2441</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0104</v>
+        <v>1.5785</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0104</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5802</v>
+        <v>4.577</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2549</v>
+        <v>3.3399</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6747</v>
+        <v>1.2371</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0836</v>
+        <v>0.7419</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-1.4121</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0387</v>
+        <v>2.154</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4592</v>
+        <v>1.7421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7087</v>
+        <v>0.1327</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7505</v>
+        <v>1.6094</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3756</v>
+        <v>-1.0002</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6638</v>
+        <v>-1.5448</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2882</v>
+        <v>0.5446</v>
       </c>
       <c r="P4" t="n">
         <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8185</v>
+        <v>1.5577</v>
       </c>
       <c r="T4" t="n">
-        <v>1.9947</v>
+        <v>1.3809</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1763</v>
+        <v>0.1768</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3115</v>
+        <v>1.9109</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9005</v>
+        <v>2.2328</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5889</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1696</v>
+        <v>3.8619</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4701</v>
+        <v>1.947</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6994</v>
+        <v>1.9149</v>
       </c>
       <c r="G5" t="n">
-        <v>2.967</v>
+        <v>2.0888</v>
       </c>
       <c r="H5" t="n">
-        <v>2.095</v>
+        <v>0.5723</v>
       </c>
       <c r="I5" t="n">
-        <v>0.872</v>
+        <v>1.5165</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0268</v>
+        <v>2.0036</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8919</v>
+        <v>0.5511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1349</v>
+        <v>1.4525</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0597</v>
+        <v>0.0852</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7968</v>
+        <v>0.0213</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7371</v>
+        <v>0.064</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3759</v>
+        <v>0.8018</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4962</v>
+        <v>0.4382</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1203</v>
+        <v>0.3637</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5785</v>
+        <v>-0.3115</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>-0.3115</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3156</v>
+        <v>3.7509</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1777</v>
+        <v>5.2522</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1379</v>
+        <v>-1.5013</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0888</v>
+        <v>2.0836</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5723</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5165</v>
+        <v>3.0387</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0036</v>
+        <v>3.4592</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5511</v>
+        <v>0.7087</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4525</v>
+        <v>2.7505</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0852</v>
+        <v>-1.3756</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0213</v>
+        <v>-1.6638</v>
       </c>
       <c r="O6" t="n">
-        <v>0.064</v>
+        <v>0.2882</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R6" t="n">
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2556</v>
+        <v>0.9893</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>0.9921</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5866</v>
+        <v>-0.0028</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3115</v>
+        <v>0.3115</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3115</v>
+        <v>1.9005</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4387</v>
+        <v>2.6995</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.223</v>
+        <v>0.1616</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6617</v>
+        <v>2.5379</v>
       </c>
       <c r="G7" t="n">
         <v>2.777</v>
@@ -1000,13 +1000,13 @@
         <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3382</v>
+        <v>-0.0775</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>0.0536</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0072</v>
+        <v>-0.1311</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9256</v>
+        <v>2.4509</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9256</v>
+        <v>0.4419</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.009</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9256</v>
+        <v>1.0043</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3005</v>
+        <v>0.3887</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>0.6156</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9256</v>
+        <v>1.3556</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3005</v>
+        <v>2.2785</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.8898</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.5385</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.0643</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2356</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.2999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8903</v>
+        <v>1.9256</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.094</v>
+        <v>1.9256</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9843</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0043</v>
+        <v>1.9256</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3887</v>
+        <v>1.3005</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6156</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3556</v>
+        <v>1.9256</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2785</v>
+        <v>1.3005</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3513</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8898</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5385</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4963</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7715</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2752</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6658</v>
+        <v>1.7867</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3491</v>
+        <v>1.4453</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3167</v>
+        <v>0.3414</v>
       </c>
       <c r="G10" t="n">
         <v>0.3482</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1447</v>
+        <v>0.2656</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1471</v>
+        <v>-0.0509</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2918</v>
+        <v>0.3165</v>
       </c>
       <c r="V10" t="n">
         <v>0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1702</v>
+        <v>-1.9007</v>
       </c>
       <c r="E11" t="n">
-        <v>0.482</v>
+        <v>0.5782</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6523</v>
+        <v>-2.4789</v>
       </c>
       <c r="G11" t="n">
         <v>0.4683</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1046</v>
+        <v>0.165</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2187</v>
+        <v>0.3149</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>-0.1499</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5339</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9451</v>
+        <v>-4.2417</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3572</v>
+        <v>-2.6291</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5879</v>
+        <v>-1.6127</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5991</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.291</v>
+        <v>0.4123</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5143</v>
+        <v>0.2138</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2233</v>
+        <v>0.1985</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>26.4981</v>
+        <v>26.7733</v>
       </c>
       <c r="E13" t="n">
-        <v>21.0728</v>
+        <v>21.3482</v>
       </c>
       <c r="F13" t="n">
-        <v>5.425099999999998</v>
+        <v>5.425000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>18.555</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4427000000000008</v>
+        <v>0.4427000000000003</v>
       </c>
       <c r="I13" t="n">
         <v>18.1123</v>
@@ -1468,13 +1468,13 @@
         <v>15.5768</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6653</v>
+        <v>3.9404</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8243</v>
+        <v>3.0999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8407000000000002</v>
+        <v>0.8406</v>
       </c>
       <c r="V13" t="n">
         <v>0.6128000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9325</v>
+        <v>3.4599</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9418</v>
+        <v>2.1341</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9908</v>
+        <v>1.3258</v>
       </c>
       <c r="G14" t="n">
         <v>2.2761</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9667</v>
+        <v>-0.4393</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6244</v>
+        <v>-0.4321</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3423</v>
+        <v>-0.0072</v>
       </c>
       <c r="V14" t="n">
         <v>1.2566</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9088</v>
+        <v>1.5996</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6065</v>
+        <v>2.9422</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6977</v>
+        <v>-1.3427</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1944</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2108</v>
+        <v>1.5458</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0164</v>
+        <v>-0.7823</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9119</v>
+        <v>2.1207</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8702</v>
+        <v>2.0374</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0417</v>
+        <v>0.0833</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7175</v>
+        <v>-1.3572</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6594</v>
+        <v>-0.4916</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0581</v>
+        <v>-0.8656</v>
       </c>
       <c r="P15" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3017</v>
+        <v>0.0089</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6109</v>
+        <v>0.1776</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3091</v>
+        <v>-0.1687</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7706</v>
+        <v>0.6439</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5632</v>
+        <v>1.1061</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0384</v>
+        <v>2.4526</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4752</v>
+        <v>-1.3465</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7635999999999999</v>
+        <v>1.1944</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5458</v>
+        <v>2.2108</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7823</v>
+        <v>-1.0164</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1207</v>
+        <v>2.9119</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0374</v>
+        <v>2.8702</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0833</v>
+        <v>0.0417</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3572</v>
+        <v>-1.7175</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4916</v>
+        <v>-0.6594</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8656</v>
+        <v>-1.0581</v>
       </c>
       <c r="P16" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0275</v>
+        <v>0.4991</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2738</v>
+        <v>0.457</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3013</v>
+        <v>0.042</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6439</v>
+        <v>-0.7706</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.7706</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3393</v>
+        <v>-0.2217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1163</v>
+        <v>-0.1722</v>
       </c>
       <c r="F18" t="n">
-        <v>0.223</v>
+        <v>-0.0495</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1314</v>
@@ -1858,13 +1858,13 @@
         <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5702</v>
+        <v>0.0092</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3107</v>
+        <v>0.0223</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2595</v>
+        <v>-0.013</v>
       </c>
       <c r="V18" t="n">
         <v>1.267</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6884</v>
+        <v>-1.7481</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1658</v>
+        <v>-2.2277</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8543</v>
+        <v>0.4796</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2251</v>
+        <v>-1.3908</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6888</v>
+        <v>0.5774</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9138</v>
+        <v>-1.9682</v>
       </c>
       <c r="J19" t="n">
-        <v>1.639</v>
+        <v>-0.9294</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8794</v>
+        <v>0.9103</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2404</v>
+        <v>-1.8397</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8641</v>
+        <v>-0.4614</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1907</v>
+        <v>-0.3329</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6735</v>
+        <v>-0.1285</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6425</v>
+        <v>-0.7238</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0166</v>
+        <v>-0.382</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6259</v>
+        <v>-0.3418</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3728</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3428</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1663</v>
+        <v>-1.8114</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9392</v>
+        <v>0.5139</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2271</v>
+        <v>-2.3253</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3908</v>
+        <v>-2.7931</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5774</v>
+        <v>-0.5907</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9682</v>
+        <v>-2.2024</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9294</v>
+        <v>0.5927</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9103</v>
+        <v>1.1921</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8397</v>
+        <v>-0.5994</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4614</v>
+        <v>-3.3858</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3329</v>
+        <v>-1.7828</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1285</v>
+        <v>-1.603</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.142</v>
+        <v>0.0089</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0935</v>
+        <v>-0.0788</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0485</v>
+        <v>0.0877</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4015</v>
+        <v>-2.0236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2255</v>
+        <v>0.0697</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6269</v>
+        <v>-2.0933</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7931</v>
+        <v>-0.2251</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5907</v>
+        <v>1.6888</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2024</v>
+        <v>-1.9138</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5927</v>
+        <v>1.639</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1921</v>
+        <v>2.8794</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5994</v>
+        <v>-1.2404</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3858</v>
+        <v>-1.8641</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7828</v>
+        <v>-1.1907</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.603</v>
+        <v>-0.6735</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
         <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5812</v>
+        <v>0.3073</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3673</v>
+        <v>-0.0795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.214</v>
+        <v>0.3869</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1267</v>
+        <v>-1.3728</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3428</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1267</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2466</v>
+        <v>-3.4803</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6642</v>
+        <v>-0.1834</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5824</v>
+        <v>-3.2969</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6351</v>
@@ -2170,13 +2170,13 @@
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7621</v>
+        <v>0.0042</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8077</v>
+        <v>-0.3269</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0455</v>
+        <v>0.3311</v>
       </c>
       <c r="V22" t="n">
         <v>0.5172</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8681</v>
+        <v>-5.64</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.427</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4411</v>
+        <v>-4.9822</v>
       </c>
       <c r="G23" t="n">
         <v>-5.076</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3984</v>
+        <v>-0.1702</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.1304</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4987</v>
+        <v>-0.0398</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9861</v>
+        <v>-7.3042</v>
       </c>
       <c r="E24" t="n">
         <v>-4.2923</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6938</v>
+        <v>-3.0119</v>
       </c>
       <c r="G24" t="n">
         <v>-4.9083</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7558</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6993</v>
+        <v>-0.0174</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5889</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.5351</v>
+        <v>-7.8795</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8469</v>
+        <v>-6.6546</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6882</v>
+        <v>-1.2249</v>
       </c>
       <c r="G25" t="n">
         <v>-4.2795</v>
@@ -2404,13 +2404,13 @@
         <v>1.4661</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5459000000000001</v>
+        <v>0.1097</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2036</v>
+        <v>-0.0113</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3423</v>
+        <v>0.121</v>
       </c>
       <c r="V25" t="n">
         <v>0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-26.4981</v>
+        <v>-23.293</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4251</v>
+        <v>-5.4253</v>
       </c>
       <c r="F26" t="n">
-        <v>-21.0729</v>
+        <v>-17.8678</v>
       </c>
       <c r="G26" t="n">
         <v>-18.555</v>
@@ -2482,13 +2482,13 @@
         <v>11.9117</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.6652</v>
+        <v>-0.4599</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8407</v>
+        <v>-0.8405999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8246</v>
+        <v>0.3808</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6125999999999998</v>
